--- a/assets/CellScores/cellscores.xlsx
+++ b/assets/CellScores/cellscores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82a9e0b2ef7d490c/Documents/GitHub/scGEAToolbox_dev/assets/CellScores/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\claude_dev\scGEAToolbox_dev\assets\CellScores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{30A5894A-51C6-4EC4-9429-8A68AF59B3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27FC8EC1-3E48-4847-B7E1-E1F0310305E1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803503EF-BFDE-4983-BD74-B4546B40FDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="276">
   <si>
     <t>ScoreType</t>
   </si>
@@ -823,6 +823,36 @@
   </si>
   <si>
     <t>WNT1, WNT2, WNT3A, WNT5A, WNT7B, FZD1, FZD2, FZD3, FZD4, FZD5, FZD6, FZD7, FZD8, FZD9, FZD10, LRP5, LRP6, CTNNB1, GSK3B, APC, AXIN1, AXIN2, DKK1, SFRP1 SFRP2</t>
+  </si>
+  <si>
+    <t>ISG15,MX1,MX2,OAS1,OAS2,OAS3,OASL,IFIT1,IFIT2,IFIT3,IFIT5,IFI6,IFI27,IFI35,IFI44,IFI44L,IFIH1,DDX58,STAT1,STAT2,IRF1,IRF7,IRF9,RSAD2,BST2,GBP1,GBP2,GBP3,GBP4,GBP5,CXCL10,CXCL9,CXCL11,CXCL16,CCL2,CCL5,TRIM5,TRIM21,TRIM22,TRIM25,TRIM56,PKR,RNASEL,ADAR,APOBEC3A,APOBEC3B,APOBEC3G,SAMHD1,HERC5,HERC6,USP18,SOCS1,SOCS3,PARP9,PARP12,PARP14,DTX3L,ZBP1,SP100,PML,TAP1,TAP2,B2M,HLA-A,HLA-B,HLA-C,HLA-E,PSMB8,PSMB9,PSMB10,NLRC5,NMI,LGALS3BP,XAF1,EPSTI1,CMPK2,LAMP3,C19orf66,IFITM1,IFITM2,IFITM3,LY6E,CH25H,TNFSF10,BATF2,SAMD9,SAMD9L</t>
+  </si>
+  <si>
+    <t>GPT5.5</t>
+  </si>
+  <si>
+    <t>(ISGs) Type I/III-enriched</t>
+  </si>
+  <si>
+    <t>(ISGs) Interferon-stimulated genes</t>
+  </si>
+  <si>
+    <t>ISG15,MX1,MX2,OAS1,OAS2,OAS3,OASL,IFIT1,IFIT2,IFIT3,IFIT5,IFI6,IFI27,IFI44,IFI44L,IFITM1,IFITM2,IFITM3,RSAD2,BST2,CH25H,LY6E,HERC5,HERC6,USP18,CMPK2,SAMD9,SAMD9L,SHFL,EPSTI1,DDX60,DDX60L,ISG20</t>
+  </si>
+  <si>
+    <t>(ISGs) Type II/IFN-γ-enriched</t>
+  </si>
+  <si>
+    <t>CXCL9,CXCL10,CXCL11,GBP1,GBP2,GBP3,GBP4,GBP5,GBP6,GBP7,CIITA,IDO1,TAP1,TAP2,PSMB8,PSMB9,PSMB10,B2M,HLA-A,HLA-B,HLA-C,HLA-E,HLA-DRA,HLA-DRB1,HLA-DPA1,HLA-DPB1,HLA-DQA1,HLA-DQB1,NLRC5,TNFSF10,CXCL16</t>
+  </si>
+  <si>
+    <t>(ISGs) Shared interferon-response genes</t>
+  </si>
+  <si>
+    <t>STAT1,STAT2,IRF1,IRF7,IRF9,DDX58,IFIH1,EIF2AK2,ADAR,RNASEL,PML,SP100,ZBP1,TRIM5,TRIM21,TRIM22,TRIM25,TRIM56,PARP9,PARP12,PARP14,DTX3L,APOBEC3A,APOBEC3B,APOBEC3G,SAMHD1,XAF1,NMI,LGALS3BP,CCL2,CCL5</t>
+  </si>
+  <si>
+    <t>ISGs</t>
   </si>
 </sst>
 </file>
@@ -923,10 +953,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1192,17 +1218,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E116"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="70.1796875" customWidth="1"/>
-    <col min="2" max="2" width="57.26953125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="42.7265625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="28.54296875" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" customWidth="1"/>
+    <col min="1" max="1" width="70.21875" customWidth="1"/>
+    <col min="2" max="2" width="57.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="42.77734375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="28.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1245,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>193</v>
       </c>
@@ -1230,7 +1256,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>185</v>
       </c>
@@ -1243,7 +1269,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>126</v>
       </c>
@@ -1255,7 +1281,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>133</v>
       </c>
@@ -1267,7 +1293,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -1281,7 +1307,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>127</v>
       </c>
@@ -1292,7 +1318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>129</v>
       </c>
@@ -1303,7 +1329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -1314,7 +1340,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>121</v>
       </c>
@@ -1325,7 +1351,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>105</v>
       </c>
@@ -1336,7 +1362,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>106</v>
       </c>
@@ -1347,7 +1373,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>108</v>
       </c>
@@ -1358,7 +1384,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1369,7 +1395,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>110</v>
       </c>
@@ -1380,7 +1406,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>111</v>
       </c>
@@ -1391,7 +1417,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -1402,7 +1428,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>114</v>
       </c>
@@ -1413,7 +1439,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>115</v>
       </c>
@@ -1424,7 +1450,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>116</v>
       </c>
@@ -1435,7 +1461,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>117</v>
       </c>
@@ -1446,7 +1472,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -1457,7 +1483,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>118</v>
       </c>
@@ -1468,7 +1494,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>119</v>
       </c>
@@ -1479,7 +1505,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1490,7 +1516,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1504,7 +1530,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1518,7 +1544,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1532,7 +1558,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1543,7 +1569,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>130</v>
       </c>
@@ -1554,7 +1580,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1565,7 +1591,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -1576,7 +1602,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -1587,7 +1613,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -1598,7 +1624,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -1609,7 +1635,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>124</v>
       </c>
@@ -1623,7 +1649,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -1634,7 +1660,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>54</v>
       </c>
@@ -1645,7 +1671,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -1656,7 +1682,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>58</v>
       </c>
@@ -1667,7 +1693,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>60</v>
       </c>
@@ -1681,7 +1707,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>62</v>
       </c>
@@ -1695,7 +1721,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>64</v>
       </c>
@@ -1709,7 +1735,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>66</v>
       </c>
@@ -1723,7 +1749,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>68</v>
       </c>
@@ -1737,7 +1763,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1751,7 +1777,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1765,7 +1791,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1779,7 +1805,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>76</v>
       </c>
@@ -1793,7 +1819,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -1807,7 +1833,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>80</v>
       </c>
@@ -1821,7 +1847,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>82</v>
       </c>
@@ -1835,7 +1861,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>84</v>
       </c>
@@ -1849,7 +1875,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>86</v>
       </c>
@@ -1863,7 +1889,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>88</v>
       </c>
@@ -1877,7 +1903,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>91</v>
       </c>
@@ -1891,7 +1917,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>93</v>
       </c>
@@ -1905,7 +1931,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>95</v>
       </c>
@@ -1919,7 +1945,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>97</v>
       </c>
@@ -1933,7 +1959,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>137</v>
       </c>
@@ -1947,7 +1973,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>140</v>
       </c>
@@ -1961,7 +1987,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>142</v>
       </c>
@@ -1975,7 +2001,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>144</v>
       </c>
@@ -1989,7 +2015,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>146</v>
       </c>
@@ -2003,7 +2029,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>148</v>
       </c>
@@ -2017,7 +2043,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>150</v>
       </c>
@@ -2031,7 +2057,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>152</v>
       </c>
@@ -2045,7 +2071,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>154</v>
       </c>
@@ -2059,7 +2085,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>156</v>
       </c>
@@ -2073,7 +2099,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>158</v>
       </c>
@@ -2087,7 +2113,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>160</v>
       </c>
@@ -2101,7 +2127,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>162</v>
       </c>
@@ -2115,7 +2141,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>164</v>
       </c>
@@ -2129,7 +2155,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>170</v>
       </c>
@@ -2143,7 +2169,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>171</v>
       </c>
@@ -2157,7 +2183,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>172</v>
       </c>
@@ -2171,7 +2197,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>173</v>
       </c>
@@ -2185,7 +2211,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>174</v>
       </c>
@@ -2199,7 +2225,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>214</v>
       </c>
@@ -2213,7 +2239,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>215</v>
       </c>
@@ -2227,7 +2253,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>216</v>
       </c>
@@ -2241,7 +2267,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>217</v>
       </c>
@@ -2255,7 +2281,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>218</v>
       </c>
@@ -2269,7 +2295,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>204</v>
       </c>
@@ -2283,7 +2309,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>205</v>
       </c>
@@ -2297,7 +2323,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>206</v>
       </c>
@@ -2311,7 +2337,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>207</v>
       </c>
@@ -2325,7 +2351,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>208</v>
       </c>
@@ -2339,7 +2365,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>209</v>
       </c>
@@ -2353,7 +2379,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>210</v>
       </c>
@@ -2367,7 +2393,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>211</v>
       </c>
@@ -2381,7 +2407,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>212</v>
       </c>
@@ -2395,7 +2421,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>213</v>
       </c>
@@ -2409,7 +2435,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>219</v>
       </c>
@@ -2423,7 +2449,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>221</v>
       </c>
@@ -2437,7 +2463,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>222</v>
       </c>
@@ -2451,7 +2477,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>226</v>
       </c>
@@ -2465,7 +2491,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>229</v>
       </c>
@@ -2479,7 +2505,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>232</v>
       </c>
@@ -2493,7 +2519,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>233</v>
       </c>
@@ -2507,7 +2533,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>234</v>
       </c>
@@ -2521,7 +2547,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>235</v>
       </c>
@@ -2535,7 +2561,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>239</v>
       </c>
@@ -2552,7 +2578,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>252</v>
       </c>
@@ -2563,7 +2589,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>253</v>
       </c>
@@ -2574,7 +2600,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>254</v>
       </c>
@@ -2585,7 +2611,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>255</v>
       </c>
@@ -2596,7 +2622,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>256</v>
       </c>
@@ -2607,7 +2633,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>257</v>
       </c>
@@ -2618,7 +2644,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>258</v>
       </c>
@@ -2629,7 +2655,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>259</v>
       </c>
@@ -2640,7 +2666,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>261</v>
       </c>
@@ -2652,6 +2678,62 @@
       </c>
       <c r="E112" t="s">
         <v>263</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>269</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D113" t="s">
+        <v>267</v>
+      </c>
+      <c r="E113" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>268</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D114" t="s">
+        <v>267</v>
+      </c>
+      <c r="E114" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>271</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D115" t="s">
+        <v>267</v>
+      </c>
+      <c r="E115" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>273</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D116" t="s">
+        <v>267</v>
+      </c>
+      <c r="E116" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/assets/CellScores/cellscores.xlsx
+++ b/assets/CellScores/cellscores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\claude_dev\scGEAToolbox_dev\assets\CellScores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803503EF-BFDE-4983-BD74-B4546B40FDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26AE1E7-09E1-416C-B705-86FF6A7672BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25703" yWindow="-1177" windowWidth="28995" windowHeight="15674" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="283">
   <si>
     <t>ScoreType</t>
   </si>
@@ -853,6 +853,27 @@
   </si>
   <si>
     <t>ISGs</t>
+  </si>
+  <si>
+    <t>(INFs) Type I</t>
+  </si>
+  <si>
+    <t>IFNA1,IFNA2,IFNA4,IFNA5,IFNA6,IFNA7,IFNA8,IFNA10,IFNA13,IFNA14,IFNA16,IFNA17,IFNA21,IFNB1,IFNE,IFNK,IFNW1</t>
+  </si>
+  <si>
+    <t>IFNG</t>
+  </si>
+  <si>
+    <t>IFNL1,IFNL2,IFNL3,IFNL4</t>
+  </si>
+  <si>
+    <t>INFs</t>
+  </si>
+  <si>
+    <t>(INFs) Type II/IFN-γ</t>
+  </si>
+  <si>
+    <t>(INFs) Type III/INF-λ</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70.21875" customWidth="1"/>
@@ -2736,6 +2757,48 @@
         <v>275</v>
       </c>
     </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>276</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D117" t="s">
+        <v>267</v>
+      </c>
+      <c r="E117" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>281</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D118" t="s">
+        <v>267</v>
+      </c>
+      <c r="E118" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>282</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D119" t="s">
+        <v>267</v>
+      </c>
+      <c r="E119" t="s">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A87" xr:uid="{16A74B7B-773D-4D2D-A1EA-E16BA506650B}">
